--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814937</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814936</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814941</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R5" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814953</v>
+        <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677539</v>
+        <v>677547</v>
       </c>
       <c r="R7" t="n">
-        <v>7109754</v>
+        <v>7109670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814934</v>
+        <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R8" t="n">
-        <v>7109670</v>
+        <v>7109754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R9" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B10" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R10" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126814975</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126814965</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814937</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814936</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814941</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814939</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B9" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R9" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R10" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126814975</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126814965</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R5" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814939</v>
+        <v>126814934</v>
       </c>
       <c r="B6" t="n">
         <v>79632</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677539</v>
+        <v>677547</v>
       </c>
       <c r="R6" t="n">
-        <v>7109781</v>
+        <v>7109670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814934</v>
+        <v>126814953</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R7" t="n">
-        <v>7109670</v>
+        <v>7109754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814953</v>
+        <v>126814978</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R8" t="n">
-        <v>7109754</v>
+        <v>7109668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R5" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814934</v>
+        <v>126814953</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109670</v>
+        <v>7109754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814953</v>
+        <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677539</v>
+        <v>677547</v>
       </c>
       <c r="R7" t="n">
-        <v>7109754</v>
+        <v>7109670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B8" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R8" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R9" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B10" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R10" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814953</v>
+        <v>126814939</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109754</v>
+        <v>7109781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814939</v>
+        <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
         <v>677539</v>
       </c>
       <c r="R8" t="n">
-        <v>7109781</v>
+        <v>7109754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R9" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R10" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R5" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814939</v>
+        <v>126814934</v>
       </c>
       <c r="B6" t="n">
         <v>79632</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677539</v>
+        <v>677547</v>
       </c>
       <c r="R6" t="n">
-        <v>7109781</v>
+        <v>7109670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814934</v>
+        <v>126814978</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677547</v>
+        <v>677588</v>
       </c>
       <c r="R7" t="n">
-        <v>7109670</v>
+        <v>7109668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814939</v>
+        <v>126814953</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>677539</v>
       </c>
       <c r="R5" t="n">
-        <v>7109781</v>
+        <v>7109754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814934</v>
+        <v>126814939</v>
       </c>
       <c r="B6" t="n">
         <v>79632</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109670</v>
+        <v>7109781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814978</v>
+        <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677588</v>
+        <v>677547</v>
       </c>
       <c r="R7" t="n">
-        <v>7109668</v>
+        <v>7109670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814953</v>
+        <v>126814978</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R8" t="n">
-        <v>7109754</v>
+        <v>7109668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814937</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814936</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814941</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814953</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R6" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814934</v>
+        <v>126814939</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R7" t="n">
-        <v>7109670</v>
+        <v>7109781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814978</v>
+        <v>126814934</v>
       </c>
       <c r="B8" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677588</v>
+        <v>677547</v>
       </c>
       <c r="R8" t="n">
-        <v>7109668</v>
+        <v>7109670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R9" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B10" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R10" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126814975</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126814965</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814953</v>
+        <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R5" t="n">
-        <v>7109754</v>
+        <v>7109668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B6" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814939</v>
+        <v>126814934</v>
       </c>
       <c r="B7" t="n">
         <v>79636</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677539</v>
+        <v>677547</v>
       </c>
       <c r="R7" t="n">
-        <v>7109781</v>
+        <v>7109670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814934</v>
+        <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677547</v>
+        <v>677539</v>
       </c>
       <c r="R8" t="n">
-        <v>7109670</v>
+        <v>7109754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B9" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R9" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R10" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R5" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R6" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814937</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814936</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814941</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R5" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B6" t="n">
-        <v>78685</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R6" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R9" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B10" t="n">
-        <v>78685</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R10" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126814975</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126814965</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26793-2025 artfynd.xlsx
+++ b/artfynd/A 26793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814937</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814936</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814941</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814978</v>
+        <v>126814939</v>
       </c>
       <c r="B5" t="n">
-        <v>78678</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677588</v>
+        <v>677539</v>
       </c>
       <c r="R5" t="n">
-        <v>7109668</v>
+        <v>7109781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814939</v>
+        <v>126814978</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677539</v>
+        <v>677588</v>
       </c>
       <c r="R6" t="n">
-        <v>7109781</v>
+        <v>7109668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>126814934</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814953</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814976</v>
+        <v>126814938</v>
       </c>
       <c r="B9" t="n">
-        <v>78678</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677541</v>
+        <v>677543</v>
       </c>
       <c r="R9" t="n">
-        <v>7109785</v>
+        <v>7109764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814938</v>
+        <v>126814976</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>78685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677543</v>
+        <v>677541</v>
       </c>
       <c r="R10" t="n">
-        <v>7109764</v>
+        <v>7109785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>126814975</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126814965</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
